--- a/data/SEMANA ATUAL/VENDAS.xlsx
+++ b/data/SEMANA ATUAL/VENDAS.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="279">
   <si>
     <t>Sigla Loja</t>
   </si>
@@ -26,6 +26,9 @@
   </si>
   <si>
     <t>21/07/2026 (Ter)</t>
+  </si>
+  <si>
+    <t>22/07/2026 (Qua)</t>
   </si>
   <si>
     <t>ABNO-RJ</t>
@@ -1213,7 +1216,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D274"/>
+  <dimension ref="A1:E274"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.7109375" customWidth="1"/>
@@ -1221,7 +1224,7 @@
     <col min="3" max="3" width="15.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1234,142 +1237,181 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" s="1">
-        <v>42164.96999999999</v>
+        <v>42164.97000000002</v>
       </c>
       <c r="D2" s="1">
         <v>42751.62</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="E2" s="1">
+        <v>39780.39999999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" s="1">
-        <v>64895.66000000001</v>
+        <v>64895.66</v>
       </c>
       <c r="D3" s="1">
-        <v>51315.06000000001</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>51315.06</v>
+      </c>
+      <c r="E3" s="1">
+        <v>66568.07000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="1">
-        <v>77580.08999999998</v>
+        <v>77580.09000000001</v>
       </c>
       <c r="D4" s="1">
-        <v>84312.23999999995</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>84378.22999999998</v>
+      </c>
+      <c r="E4" s="1">
+        <v>83739.02999999998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" s="1">
-        <v>47734.78000000001</v>
+        <v>47734.78</v>
       </c>
       <c r="D5" s="1">
-        <v>41102.27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>41180.25999999999</v>
+      </c>
+      <c r="E5" s="1">
+        <v>52680.15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C6" s="1">
         <v>44943.7</v>
       </c>
       <c r="D6" s="1">
-        <v>52150.45000000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+        <v>52230.81</v>
+      </c>
+      <c r="E6" s="1">
+        <v>43661.91000000002</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C7" s="1">
-        <v>62249.61</v>
+        <v>62249.60999999999</v>
       </c>
       <c r="D7" s="1">
         <v>54645.87999999999</v>
       </c>
-    </row>
-    <row r="8" spans="1:4">
+      <c r="E7" s="1">
+        <v>57957.80999999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C8" s="1">
-        <v>36327.45000000001</v>
+        <v>36327.45</v>
       </c>
       <c r="D8" s="1">
-        <v>36621</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+        <v>36621.00000000001</v>
+      </c>
+      <c r="E8" s="1">
+        <v>35271.99999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C9" s="1">
-        <v>45442.82000000002</v>
+        <v>45442.82000000001</v>
       </c>
       <c r="D9" s="1">
         <v>40078.85999999999</v>
       </c>
-    </row>
-    <row r="10" spans="1:4">
+      <c r="E9" s="1">
+        <v>33015.55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C10" s="1">
         <v>19267.79</v>
       </c>
       <c r="D10" s="1">
-        <v>18098.74000000001</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
+        <v>18098.74</v>
+      </c>
+      <c r="E10" s="1">
+        <v>21225.59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C11" s="1">
-        <v>70423.36</v>
+        <v>70423.35999999999</v>
       </c>
       <c r="D11" s="1">
-        <v>73788.03</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
+        <v>73813.01999999997</v>
+      </c>
+      <c r="E11" s="1">
+        <v>70351.53</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C12" s="1">
-        <v>38725.31</v>
+        <v>38725.30999999998</v>
       </c>
       <c r="D12" s="1">
         <v>37190.23</v>
       </c>
-    </row>
-    <row r="13" spans="1:4">
+      <c r="E12" s="1">
+        <v>33690.77</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C13" s="1">
-        <v>54161.08999999999</v>
+        <v>54161.09</v>
       </c>
       <c r="D13" s="1">
-        <v>52834.50999999999</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
+        <v>52834.51</v>
+      </c>
+      <c r="E13" s="1">
+        <v>45810.36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C14" s="1">
         <v>58465.55</v>
@@ -1377,54 +1419,69 @@
       <c r="D14" s="1">
         <v>61219.33</v>
       </c>
-    </row>
-    <row r="15" spans="1:4">
+      <c r="E14" s="1">
+        <v>53388.04000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C15" s="1">
-        <v>94771.99999999999</v>
+        <v>94771.99999999997</v>
       </c>
       <c r="D15" s="1">
-        <v>95744.16999999998</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
+        <v>95744.16999999997</v>
+      </c>
+      <c r="E15" s="1">
+        <v>81429.55999999998</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C16" s="1">
         <v>21052.68</v>
       </c>
       <c r="D16" s="1">
-        <v>21387.77000000001</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
+        <v>21387.77</v>
+      </c>
+      <c r="E16" s="1">
+        <v>22895.47</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C17" s="1">
         <v>39653.4</v>
       </c>
       <c r="D17" s="1">
-        <v>50415.94000000001</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
+        <v>50415.94000000002</v>
+      </c>
+      <c r="E17" s="1">
+        <v>46717.19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C18" s="1">
         <v>31389.73000000001</v>
       </c>
       <c r="D18" s="1">
-        <v>24760.87</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
+        <v>24760.87000000001</v>
+      </c>
+      <c r="E18" s="1">
+        <v>26233.4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C19" s="1">
         <v>40336.31</v>
@@ -1432,43 +1489,55 @@
       <c r="D19" s="1">
         <v>31679.42</v>
       </c>
-    </row>
-    <row r="20" spans="1:4">
+      <c r="E19" s="1">
+        <v>40910.32</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C20" s="1">
-        <v>62848.23000000001</v>
+        <v>62848.23</v>
       </c>
       <c r="D20" s="1">
-        <v>61781.33</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
+        <v>61781.33000000002</v>
+      </c>
+      <c r="E20" s="1">
+        <v>50157.33</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C21" s="1">
-        <v>48637.24000000001</v>
+        <v>48637.24</v>
       </c>
       <c r="D21" s="1">
         <v>24266.45</v>
       </c>
-    </row>
-    <row r="22" spans="1:4">
+      <c r="E21" s="1">
+        <v>17593.8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C22" s="1">
         <v>18986.23</v>
       </c>
       <c r="D22" s="1">
-        <v>23222.01999999999</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
+        <v>23222.02</v>
+      </c>
+      <c r="E22" s="1">
+        <v>18377.11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C23" s="1">
         <v>16141.87</v>
@@ -1476,43 +1545,55 @@
       <c r="D23" s="1">
         <v>14622.57</v>
       </c>
-    </row>
-    <row r="24" spans="1:4">
+      <c r="E23" s="1">
+        <v>11534.32999999999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C24" s="1">
-        <v>26795.21</v>
+        <v>26795.21000000001</v>
       </c>
       <c r="D24" s="1">
-        <v>26688.68</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
+        <v>26733.65</v>
+      </c>
+      <c r="E24" s="1">
+        <v>24390.34</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C25" s="1">
         <v>18126.59</v>
       </c>
       <c r="D25" s="1">
-        <v>21052.22000000001</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
+        <v>21052.22</v>
+      </c>
+      <c r="E25" s="1">
+        <v>17085.58</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C26" s="1">
-        <v>86266.64000000001</v>
+        <v>86266.63999999996</v>
       </c>
       <c r="D26" s="1">
-        <v>93446.89999999995</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
+        <v>93446.89999999997</v>
+      </c>
+      <c r="E26" s="1">
+        <v>87328.48</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
       <c r="A27" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C27" s="1">
         <v>26912.5</v>
@@ -1520,10 +1601,13 @@
       <c r="D27" s="1">
         <v>27142.08</v>
       </c>
-    </row>
-    <row r="28" spans="1:4">
+      <c r="E27" s="1">
+        <v>22551.22</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C28" s="1">
         <v>67076.31999999999</v>
@@ -1531,21 +1615,27 @@
       <c r="D28" s="1">
         <v>60700.63999999998</v>
       </c>
-    </row>
-    <row r="29" spans="1:4">
+      <c r="E28" s="1">
+        <v>60486.58</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C29" s="1">
-        <v>95356.99999999996</v>
+        <v>95356.99999999999</v>
       </c>
       <c r="D29" s="1">
-        <v>121560.2999999999</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
+        <v>122095.7999999999</v>
+      </c>
+      <c r="E29" s="1">
+        <v>116679.1699999999</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C30" s="1">
         <v>25736.7</v>
@@ -1553,21 +1643,27 @@
       <c r="D30" s="1">
         <v>26293.56</v>
       </c>
-    </row>
-    <row r="31" spans="1:4">
+      <c r="E30" s="1">
+        <v>27642.7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
       <c r="A31" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C31" s="1">
-        <v>23573.61000000001</v>
+        <v>23573.61</v>
       </c>
       <c r="D31" s="1">
         <v>25320.2</v>
       </c>
-    </row>
-    <row r="32" spans="1:4">
+      <c r="E31" s="1">
+        <v>23564.03</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
       <c r="A32" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C32" s="1">
         <v>88091.36999999998</v>
@@ -1575,65 +1671,83 @@
       <c r="D32" s="1">
         <v>80946.90999999997</v>
       </c>
-    </row>
-    <row r="33" spans="1:4">
+      <c r="E32" s="1">
+        <v>88425.95999999998</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
       <c r="A33" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C33" s="1">
         <v>82125.11</v>
       </c>
       <c r="D33" s="1">
-        <v>87478.92999999999</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4">
+        <v>87478.93000000001</v>
+      </c>
+      <c r="E33" s="1">
+        <v>90355.22</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
       <c r="A34" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C34" s="1">
-        <v>108289.41</v>
+        <v>108289.4099999999</v>
       </c>
       <c r="D34" s="1">
-        <v>97039.62999999996</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
+        <v>98879.65999999997</v>
+      </c>
+      <c r="E34" s="1">
+        <v>112854.23</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
       <c r="A35" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C35" s="1">
-        <v>27296.35000000001</v>
+        <v>27296.35</v>
       </c>
       <c r="D35" s="1">
-        <v>29921.51000000001</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
+        <v>29921.51</v>
+      </c>
+      <c r="E35" s="1">
+        <v>27219.12</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
       <c r="A36" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C36" s="1">
-        <v>70523.91000000002</v>
+        <v>70523.90999999999</v>
       </c>
       <c r="D36" s="1">
-        <v>58454.80000000001</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4">
+        <v>58454.8</v>
+      </c>
+      <c r="E36" s="1">
+        <v>62836.99999999999</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
       <c r="A37" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C37" s="1">
-        <v>103478.7899999999</v>
+        <v>103478.79</v>
       </c>
       <c r="D37" s="1">
         <v>107966.04</v>
       </c>
-    </row>
-    <row r="38" spans="1:4">
+      <c r="E37" s="1">
+        <v>90283.88999999998</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
       <c r="A38" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C38" s="1">
         <v>22429.38</v>
@@ -1641,10 +1755,13 @@
       <c r="D38" s="1">
         <v>18198.03</v>
       </c>
-    </row>
-    <row r="39" spans="1:4">
+      <c r="E38" s="1">
+        <v>15915.91</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C39" s="1">
         <v>16712.79</v>
@@ -1652,186 +1769,237 @@
       <c r="D39" s="1">
         <v>13894.19</v>
       </c>
-    </row>
-    <row r="40" spans="1:4">
+      <c r="E39" s="1">
+        <v>20321.02</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
       <c r="A40" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C40" s="1">
-        <v>48834.97</v>
+        <v>48834.97000000001</v>
       </c>
       <c r="D40" s="1">
-        <v>51916.31999999999</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4">
+        <v>51916.32</v>
+      </c>
+      <c r="E40" s="1">
+        <v>53909.15000000002</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
       <c r="A41" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C41" s="1">
-        <v>57478.04</v>
+        <v>57478.03999999999</v>
       </c>
       <c r="D41" s="1">
-        <v>59664.84</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4">
+        <v>59664.84000000001</v>
+      </c>
+      <c r="E41" s="1">
+        <v>50747</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
       <c r="A42" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C42" s="1">
-        <v>55331.29</v>
+        <v>55331.28999999999</v>
       </c>
       <c r="D42" s="1">
-        <v>57567.81999999999</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4">
+        <v>57567.82000000001</v>
+      </c>
+      <c r="E42" s="1">
+        <v>49732.76999999999</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
       <c r="A43" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C43" s="1">
         <v>19224.32</v>
       </c>
       <c r="D43" s="1">
-        <v>21684.78</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4">
+        <v>21694.34</v>
+      </c>
+      <c r="E43" s="1">
+        <v>16156.64</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
       <c r="A44" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C44" s="1">
-        <v>50207.49000000001</v>
+        <v>50207.49000000002</v>
       </c>
       <c r="D44" s="1">
         <v>58630.06</v>
       </c>
-    </row>
-    <row r="45" spans="1:4">
+      <c r="E44" s="1">
+        <v>66868.84</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
       <c r="A45" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C45" s="1">
-        <v>91437.49999999999</v>
+        <v>91437.50000000003</v>
       </c>
       <c r="D45" s="1">
-        <v>91464.2</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4">
+        <v>91464.19999999998</v>
+      </c>
+      <c r="E45" s="1">
+        <v>86018.70999999999</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
       <c r="A46" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C46" s="1">
-        <v>96965.29999999996</v>
+        <v>96965.29999999999</v>
       </c>
       <c r="D46" s="1">
-        <v>88251.92999999998</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4">
+        <v>88251.92999999996</v>
+      </c>
+      <c r="E46" s="1">
+        <v>93364.25999999997</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
       <c r="A47" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C47" s="1">
-        <v>25734.52000000001</v>
+        <v>25734.52</v>
       </c>
       <c r="D47" s="1">
-        <v>30939.54</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4">
+        <v>30939.54000000001</v>
+      </c>
+      <c r="E47" s="1">
+        <v>28554.86</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
       <c r="A48" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C48" s="1">
-        <v>65683.30000000002</v>
+        <v>65683.29999999999</v>
       </c>
       <c r="D48" s="1">
-        <v>68950.58999999998</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4">
+        <v>69483.87999999999</v>
+      </c>
+      <c r="E48" s="1">
+        <v>64836.94</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
       <c r="A49" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C49" s="1">
-        <v>100008.5</v>
+        <v>100008.4999999999</v>
       </c>
       <c r="D49" s="1">
         <v>90700.88999999997</v>
       </c>
-    </row>
-    <row r="50" spans="1:4">
+      <c r="E49" s="1">
+        <v>85990.99999999996</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
       <c r="A50" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C50" s="1">
         <v>17056.68</v>
       </c>
       <c r="D50" s="1">
-        <v>17320.92</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4">
+        <v>17320.92000000001</v>
+      </c>
+      <c r="E50" s="1">
+        <v>16094.78</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
       <c r="A51" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C51" s="1">
-        <v>35838.17999999999</v>
+        <v>35838.18000000001</v>
       </c>
       <c r="D51" s="1">
         <v>43839.25</v>
       </c>
-    </row>
-    <row r="52" spans="1:4">
+      <c r="E51" s="1">
+        <v>39037.99000000001</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
       <c r="A52" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C52" s="1">
         <v>22154.61</v>
       </c>
       <c r="D52" s="1">
-        <v>27352.47</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4">
+        <v>27430.44000000001</v>
+      </c>
+      <c r="E52" s="1">
+        <v>31213.17999999999</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
       <c r="A53" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C53" s="1">
-        <v>41040.21999999999</v>
+        <v>41040.22000000001</v>
       </c>
       <c r="D53" s="1">
         <v>36926.63</v>
       </c>
-    </row>
-    <row r="54" spans="1:4">
+      <c r="E53" s="1">
+        <v>28194.02</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
       <c r="A54" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C54" s="1">
-        <v>14026.61999999999</v>
+        <v>14026.62</v>
       </c>
       <c r="D54" s="1">
         <v>12760.55</v>
       </c>
-    </row>
-    <row r="55" spans="1:4">
+      <c r="E54" s="1">
+        <v>14818.45</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
       <c r="A55" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C55" s="1">
-        <v>27594.91</v>
+        <v>27594.91000000001</v>
       </c>
       <c r="D55" s="1">
         <v>22138.97000000001</v>
       </c>
-    </row>
-    <row r="56" spans="1:4">
+      <c r="E55" s="1">
+        <v>27969.39</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
       <c r="A56" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C56" s="1">
         <v>42885.74999999999</v>
@@ -1839,43 +2007,55 @@
       <c r="D56" s="1">
         <v>32558.20000000001</v>
       </c>
-    </row>
-    <row r="57" spans="1:4">
+      <c r="E56" s="1">
+        <v>39093.62</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
       <c r="A57" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D57" s="1">
         <v>847921.5900000001</v>
       </c>
-    </row>
-    <row r="58" spans="1:4">
+      <c r="E57" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
       <c r="A58" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C58" s="1">
         <v>312669.3799999999</v>
       </c>
       <c r="D58" s="1">
-        <v>290056.6899999999</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4">
+        <v>290056.69</v>
+      </c>
+      <c r="E58" s="1">
+        <v>286403.0100000001</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
       <c r="A59" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C59" s="1">
         <v>37649.69</v>
       </c>
       <c r="D59" s="1">
-        <v>31031.98999999999</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4">
+        <v>31031.99</v>
+      </c>
+      <c r="E59" s="1">
+        <v>26891.16000000001</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
       <c r="A60" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C60" s="1">
         <v>39881.60000000001</v>
@@ -1883,21 +2063,27 @@
       <c r="D60" s="1">
         <v>33546.10000000001</v>
       </c>
-    </row>
-    <row r="61" spans="1:4">
+      <c r="E60" s="1">
+        <v>45874.22</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
       <c r="A61" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D61" s="1">
-        <v>5094.409999999998</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4">
+        <v>5094.409999999999</v>
+      </c>
+      <c r="E61" s="1">
+        <v>1594.75</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
       <c r="A62" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C62" s="1">
         <v>12369.26</v>
@@ -1905,21 +2091,27 @@
       <c r="D62" s="1">
         <v>15359.5</v>
       </c>
-    </row>
-    <row r="63" spans="1:4">
+      <c r="E62" s="1">
+        <v>13570.92</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
       <c r="A63" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C63" s="1">
-        <v>83499.19999999998</v>
+        <v>83499.2</v>
       </c>
       <c r="D63" s="1">
-        <v>65211.25</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4">
+        <v>65211.24999999999</v>
+      </c>
+      <c r="E63" s="1">
+        <v>67382.65000000001</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
       <c r="A64" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C64" s="1">
         <v>17384.37</v>
@@ -1927,10 +2119,13 @@
       <c r="D64" s="1">
         <v>16636.31</v>
       </c>
-    </row>
-    <row r="65" spans="1:4">
+      <c r="E64" s="1">
+        <v>15312.57</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
       <c r="A65" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C65" s="1">
         <v>51916.51</v>
@@ -1938,10 +2133,13 @@
       <c r="D65" s="1">
         <v>53893.23000000001</v>
       </c>
-    </row>
-    <row r="66" spans="1:4">
+      <c r="E65" s="1">
+        <v>63197.98999999999</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
       <c r="A66" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C66" s="1">
         <v>43764.26</v>
@@ -1949,32 +2147,41 @@
       <c r="D66" s="1">
         <v>41495.38</v>
       </c>
-    </row>
-    <row r="67" spans="1:4">
+      <c r="E66" s="1">
+        <v>43521.38000000001</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
       <c r="A67" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C67" s="1">
         <v>14259.38</v>
       </c>
       <c r="D67" s="1">
-        <v>14555.73999999999</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4">
+        <v>14555.74</v>
+      </c>
+      <c r="E67" s="1">
+        <v>14055.06</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
       <c r="A68" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C68" s="1">
         <v>36527.51</v>
       </c>
       <c r="D68" s="1">
-        <v>30242.9</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4">
+        <v>30242.90000000001</v>
+      </c>
+      <c r="E68" s="1">
+        <v>39454.91</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
       <c r="A69" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C69" s="1">
         <v>32148.09</v>
@@ -1982,87 +2189,111 @@
       <c r="D69" s="1">
         <v>22240.59</v>
       </c>
-    </row>
-    <row r="70" spans="1:4">
+      <c r="E69" s="1">
+        <v>24560.3</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
       <c r="A70" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C70" s="1">
-        <v>32586.26</v>
+        <v>32586.25999999999</v>
       </c>
       <c r="D70" s="1">
-        <v>40672.07</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4">
+        <v>41141.01000000001</v>
+      </c>
+      <c r="E70" s="1">
+        <v>34280.27</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
       <c r="A71" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C71" s="1">
-        <v>34649.32</v>
+        <v>34649.32000000001</v>
       </c>
       <c r="D71" s="1">
-        <v>34968.03000000001</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4">
+        <v>34968.03</v>
+      </c>
+      <c r="E71" s="1">
+        <v>28520.08</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
       <c r="A72" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C72" s="1">
-        <v>61975.17999999999</v>
+        <v>61975.18</v>
       </c>
       <c r="D72" s="1">
-        <v>64940.33999999997</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4">
+        <v>65695.25</v>
+      </c>
+      <c r="E72" s="1">
+        <v>62401.72999999999</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
       <c r="A73" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C73" s="1">
-        <v>19686.57000000001</v>
+        <v>19686.57</v>
       </c>
       <c r="D73" s="1">
         <v>22356.93</v>
       </c>
-    </row>
-    <row r="74" spans="1:4">
+      <c r="E73" s="1">
+        <v>23111.71</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
       <c r="A74" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C74" s="1">
-        <v>28679.72999999999</v>
+        <v>28679.73</v>
       </c>
       <c r="D74" s="1">
-        <v>26152.83000000001</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4">
+        <v>26152.83</v>
+      </c>
+      <c r="E74" s="1">
+        <v>19746.37</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
       <c r="A75" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C75" s="1">
-        <v>39056.46000000001</v>
+        <v>39056.46</v>
       </c>
       <c r="D75" s="1">
         <v>38243.27</v>
       </c>
-    </row>
-    <row r="76" spans="1:4">
+      <c r="E75" s="1">
+        <v>34976.64</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
       <c r="A76" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C76" s="1">
         <v>36721.02</v>
       </c>
       <c r="D76" s="1">
-        <v>34960.44999999999</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4">
+        <v>34960.45</v>
+      </c>
+      <c r="E76" s="1">
+        <v>35987.71999999999</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
       <c r="A77" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C77" s="1">
         <v>38639.73</v>
@@ -2070,142 +2301,181 @@
       <c r="D77" s="1">
         <v>25811.78000000001</v>
       </c>
-    </row>
-    <row r="78" spans="1:4">
+      <c r="E77" s="1">
+        <v>30977.36000000001</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
       <c r="A78" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C78" s="1">
-        <v>45652.27999999999</v>
+        <v>45652.28</v>
       </c>
       <c r="D78" s="1">
         <v>35823.12</v>
       </c>
-    </row>
-    <row r="79" spans="1:4">
+      <c r="E78" s="1">
+        <v>50557.17999999999</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
       <c r="A79" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C79" s="1">
-        <v>49697.08000000001</v>
+        <v>49697.07999999999</v>
       </c>
       <c r="D79" s="1">
-        <v>47877.79000000001</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4">
+        <v>47877.78999999999</v>
+      </c>
+      <c r="E79" s="1">
+        <v>53617.71999999999</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
       <c r="A80" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C80" s="1">
-        <v>29826.58999999999</v>
+        <v>29826.59</v>
       </c>
       <c r="D80" s="1">
         <v>22819.79</v>
       </c>
-    </row>
-    <row r="81" spans="1:4">
+      <c r="E80" s="1">
+        <v>26521.97</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
       <c r="A81" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C81" s="1">
-        <v>36870.44</v>
+        <v>36870.44000000001</v>
       </c>
       <c r="D81" s="1">
         <v>33843.96</v>
       </c>
-    </row>
-    <row r="82" spans="1:4">
+      <c r="E81" s="1">
+        <v>32005.18000000001</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
       <c r="A82" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C82" s="1">
         <v>43686.63</v>
       </c>
       <c r="D82" s="1">
-        <v>42083.14999999999</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4">
+        <v>42083.15</v>
+      </c>
+      <c r="E82" s="1">
+        <v>32422.92</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
       <c r="A83" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C83" s="1">
         <v>39888.56</v>
       </c>
       <c r="D83" s="1">
-        <v>38405.28</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4">
+        <v>38405.28000000001</v>
+      </c>
+      <c r="E83" s="1">
+        <v>34063.68000000001</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
       <c r="A84" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C84" s="1">
         <v>29783.01</v>
       </c>
       <c r="D84" s="1">
-        <v>22295.6</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4">
+        <v>22295.60000000001</v>
+      </c>
+      <c r="E84" s="1">
+        <v>28190.96</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
       <c r="A85" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C85" s="1">
-        <v>32074.27000000001</v>
+        <v>32074.27</v>
       </c>
       <c r="D85" s="1">
-        <v>26552.06999999999</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4">
+        <v>26552.07</v>
+      </c>
+      <c r="E85" s="1">
+        <v>24129.4</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
       <c r="A86" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C86" s="1">
         <v>40172.59</v>
       </c>
       <c r="D86" s="1">
-        <v>42177.86000000001</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4">
+        <v>42177.85999999999</v>
+      </c>
+      <c r="E86" s="1">
+        <v>35740.93000000001</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
       <c r="A87" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C87" s="1">
         <v>148722.0499999999</v>
       </c>
       <c r="D87" s="1">
-        <v>138234.76</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4">
+        <v>138899.8799999999</v>
+      </c>
+      <c r="E87" s="1">
+        <v>134800.6199999999</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
       <c r="A88" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C88" s="1">
         <v>35293.45</v>
       </c>
       <c r="D88" s="1">
-        <v>23334.72999999999</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4">
+        <v>23334.73000000001</v>
+      </c>
+      <c r="E88" s="1">
+        <v>35480.84</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
       <c r="A89" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C89" s="1">
         <v>19554.82</v>
       </c>
       <c r="D89" s="1">
-        <v>18660.19</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4">
+        <v>18720.16999999999</v>
+      </c>
+      <c r="E89" s="1">
+        <v>20902.09</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
       <c r="A90" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C90" s="1">
         <v>15194.11</v>
@@ -2213,10 +2483,13 @@
       <c r="D90" s="1">
         <v>10676.01</v>
       </c>
-    </row>
-    <row r="91" spans="1:4">
+      <c r="E90" s="1">
+        <v>11043.48</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
       <c r="A91" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C91" s="1">
         <v>21467.64</v>
@@ -2224,241 +2497,307 @@
       <c r="D91" s="1">
         <v>21830.62</v>
       </c>
-    </row>
-    <row r="92" spans="1:4">
+      <c r="E91" s="1">
+        <v>21078.35000000001</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
       <c r="A92" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C92" s="1">
-        <v>60038.81999999999</v>
+        <v>60038.82000000001</v>
       </c>
       <c r="D92" s="1">
-        <v>56230.47999999999</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4">
+        <v>56230.48</v>
+      </c>
+      <c r="E92" s="1">
+        <v>55009.39000000001</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
       <c r="A93" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C93" s="1">
-        <v>35434.10999999999</v>
+        <v>35434.11000000001</v>
       </c>
       <c r="D93" s="1">
-        <v>33927.5</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4">
+        <v>33927.49999999999</v>
+      </c>
+      <c r="E93" s="1">
+        <v>28642.15</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
       <c r="A94" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C94" s="1">
-        <v>49358.08000000001</v>
+        <v>49358.07999999999</v>
       </c>
       <c r="D94" s="1">
-        <v>52125.18</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4">
+        <v>52125.18000000001</v>
+      </c>
+      <c r="E94" s="1">
+        <v>46474.13000000002</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
       <c r="A95" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C95" s="1">
         <v>21080.81</v>
       </c>
       <c r="D95" s="1">
-        <v>18138.49000000001</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4">
+        <v>18138.49</v>
+      </c>
+      <c r="E95" s="1">
+        <v>21586.54</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
       <c r="A96" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C96" s="1">
-        <v>66491.62</v>
+        <v>66491.62000000001</v>
       </c>
       <c r="D96" s="1">
-        <v>51078.09000000002</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4">
+        <v>51078.09</v>
+      </c>
+      <c r="E96" s="1">
+        <v>65606.3</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
       <c r="A97" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C97" s="1">
-        <v>95070.72999999998</v>
+        <v>95070.72999999995</v>
       </c>
       <c r="D97" s="1">
-        <v>80877.01999999999</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4">
+        <v>80877.01999999997</v>
+      </c>
+      <c r="E97" s="1">
+        <v>77934.95999999998</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5">
       <c r="A98" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C98" s="1">
-        <v>57440.51999999998</v>
+        <v>57440.52000000001</v>
       </c>
       <c r="D98" s="1">
-        <v>52852.92000000001</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4">
+        <v>52852.91999999998</v>
+      </c>
+      <c r="E98" s="1">
+        <v>63480.55</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
       <c r="A99" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C99" s="1">
-        <v>62892.64000000001</v>
+        <v>62892.63999999998</v>
       </c>
       <c r="D99" s="1">
         <v>62860.44</v>
       </c>
-    </row>
-    <row r="100" spans="1:4">
+      <c r="E99" s="1">
+        <v>71278.45</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5">
       <c r="A100" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C100" s="1">
         <v>41258.78000000001</v>
       </c>
       <c r="D100" s="1">
-        <v>40426.64</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4">
+        <v>40426.64000000001</v>
+      </c>
+      <c r="E100" s="1">
+        <v>43093.7</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5">
       <c r="A101" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C101" s="1">
-        <v>23934.85</v>
+        <v>23934.85000000001</v>
       </c>
       <c r="D101" s="1">
-        <v>24060.93</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4">
+        <v>24119.92</v>
+      </c>
+      <c r="E101" s="1">
+        <v>20478.97</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5">
       <c r="A102" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C102" s="1">
         <v>22850.96</v>
       </c>
       <c r="D102" s="1">
-        <v>21921.61999999999</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4">
+        <v>21921.62000000001</v>
+      </c>
+      <c r="E102" s="1">
+        <v>23688.46</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5">
       <c r="A103" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C103" s="1">
         <v>21808.89</v>
       </c>
       <c r="D103" s="1">
-        <v>24429.79</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4">
+        <v>24511.69</v>
+      </c>
+      <c r="E103" s="1">
+        <v>32486.81</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5">
       <c r="A104" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C104" s="1">
-        <v>50147.59999999998</v>
+        <v>50147.60000000001</v>
       </c>
       <c r="D104" s="1">
-        <v>41877.71</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4">
+        <v>41877.71000000001</v>
+      </c>
+      <c r="E104" s="1">
+        <v>41572.19</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5">
       <c r="A105" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C105" s="1">
-        <v>30700.59000000001</v>
+        <v>30700.59</v>
       </c>
       <c r="D105" s="1">
-        <v>28850.24000000001</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4">
+        <v>28850.23999999999</v>
+      </c>
+      <c r="E105" s="1">
+        <v>27202.97</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5">
       <c r="A106" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C106" s="1">
-        <v>19122.55000000001</v>
+        <v>19122.55</v>
       </c>
       <c r="D106" s="1">
         <v>22369.47</v>
       </c>
-    </row>
-    <row r="107" spans="1:4">
+      <c r="E106" s="1">
+        <v>15804.58</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5">
       <c r="A107" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C107" s="1">
-        <v>25312.18</v>
+        <v>25312.18000000001</v>
       </c>
       <c r="D107" s="1">
         <v>23677.19</v>
       </c>
-    </row>
-    <row r="108" spans="1:4">
+      <c r="E107" s="1">
+        <v>29405.55999999999</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5">
       <c r="A108" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C108" s="1">
-        <v>43072.08</v>
+        <v>43072.07999999999</v>
       </c>
       <c r="D108" s="1">
-        <v>39030.51000000002</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4">
+        <v>39030.50999999999</v>
+      </c>
+      <c r="E108" s="1">
+        <v>38695.36</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5">
       <c r="A109" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C109" s="1">
-        <v>24853.79000000001</v>
+        <v>24853.79</v>
       </c>
       <c r="D109" s="1">
         <v>26404.85</v>
       </c>
-    </row>
-    <row r="110" spans="1:4">
+      <c r="E109" s="1">
+        <v>25924.98</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5">
       <c r="A110" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C110" s="1">
-        <v>44651.92</v>
+        <v>44651.92000000001</v>
       </c>
       <c r="D110" s="1">
-        <v>48642.01000000002</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4">
+        <v>48642.00999999999</v>
+      </c>
+      <c r="E110" s="1">
+        <v>53168.46999999999</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5">
       <c r="A111" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C111" s="1">
         <v>29726.62</v>
       </c>
       <c r="D111" s="1">
-        <v>27224.41999999999</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4">
+        <v>27224.42000000001</v>
+      </c>
+      <c r="E111" s="1">
+        <v>24265.24000000001</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5">
       <c r="A112" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C112" s="1">
         <v>28292.05</v>
       </c>
       <c r="D112" s="1">
-        <v>27748.09</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4">
+        <v>27748.08999999999</v>
+      </c>
+      <c r="E112" s="1">
+        <v>25107.39999999999</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5">
       <c r="A113" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C113" s="1">
         <v>21797.86</v>
@@ -2466,10 +2805,13 @@
       <c r="D113" s="1">
         <v>21808</v>
       </c>
-    </row>
-    <row r="114" spans="1:4">
+      <c r="E113" s="1">
+        <v>19943.18</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5">
       <c r="A114" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C114" s="1">
         <v>28996.46</v>
@@ -2477,32 +2819,41 @@
       <c r="D114" s="1">
         <v>21280.99</v>
       </c>
-    </row>
-    <row r="115" spans="1:4">
+      <c r="E114" s="1">
+        <v>28402.08</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5">
       <c r="A115" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C115" s="1">
-        <v>28833.08000000001</v>
+        <v>28833.08</v>
       </c>
       <c r="D115" s="1">
         <v>23664.56</v>
       </c>
-    </row>
-    <row r="116" spans="1:4">
+      <c r="E115" s="1">
+        <v>30914.94</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5">
       <c r="A116" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C116" s="1">
-        <v>7792.22</v>
+        <v>7792.219999999998</v>
       </c>
       <c r="D116" s="1">
         <v>8933.369999999999</v>
       </c>
-    </row>
-    <row r="117" spans="1:4">
+      <c r="E116" s="1">
+        <v>9889.320000000002</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5">
       <c r="A117" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C117" s="1">
         <v>22398.22</v>
@@ -2510,54 +2861,69 @@
       <c r="D117" s="1">
         <v>19231.9</v>
       </c>
-    </row>
-    <row r="118" spans="1:4">
+      <c r="E117" s="1">
+        <v>22250.16</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5">
       <c r="A118" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C118" s="1">
         <v>19750.16</v>
       </c>
       <c r="D118" s="1">
-        <v>22227.65999999999</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4">
+        <v>22227.66</v>
+      </c>
+      <c r="E118" s="1">
+        <v>18003.95</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5">
       <c r="A119" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C119" s="1">
-        <v>43707.49</v>
+        <v>43707.49000000001</v>
       </c>
       <c r="D119" s="1">
-        <v>27255.56000000001</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4">
+        <v>27255.56</v>
+      </c>
+      <c r="E119" s="1">
+        <v>32141.00000000001</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5">
       <c r="A120" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C120" s="1">
         <v>28984.14</v>
       </c>
       <c r="D120" s="1">
-        <v>20512.39000000001</v>
-      </c>
-    </row>
-    <row r="121" spans="1:4">
+        <v>20512.39</v>
+      </c>
+      <c r="E120" s="1">
+        <v>19687.63</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5">
       <c r="A121" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C121" s="1">
-        <v>111868.47</v>
+        <v>111868.4699999999</v>
       </c>
       <c r="D121" s="1">
-        <v>86454.17</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4">
+        <v>86454.16999999998</v>
+      </c>
+      <c r="E121" s="1">
+        <v>107572.25</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5">
       <c r="A122" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C122" s="1">
         <v>21460.08</v>
@@ -2565,43 +2931,55 @@
       <c r="D122" s="1">
         <v>20167.15</v>
       </c>
-    </row>
-    <row r="123" spans="1:4">
+      <c r="E122" s="1">
+        <v>19968.4</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5">
       <c r="A123" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C123" s="1">
         <v>44840.94</v>
       </c>
       <c r="D123" s="1">
-        <v>41324.95999999999</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4">
+        <v>41324.96000000001</v>
+      </c>
+      <c r="E123" s="1">
+        <v>37829.16</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5">
       <c r="A124" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C124" s="1">
         <v>34545.96</v>
       </c>
       <c r="D124" s="1">
-        <v>38709.01</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4">
+        <v>38709.00999999999</v>
+      </c>
+      <c r="E124" s="1">
+        <v>29255.17</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5">
       <c r="A125" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C125" s="1">
         <v>28848.63</v>
       </c>
       <c r="D125" s="1">
-        <v>29234.64999999999</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4">
+        <v>29234.65</v>
+      </c>
+      <c r="E125" s="1">
+        <v>33129.84000000001</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5">
       <c r="A126" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C126" s="1">
         <v>27846.56</v>
@@ -2609,10 +2987,13 @@
       <c r="D126" s="1">
         <v>20545.83</v>
       </c>
-    </row>
-    <row r="127" spans="1:4">
+      <c r="E126" s="1">
+        <v>18465.21</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5">
       <c r="A127" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C127" s="1">
         <v>35023.12</v>
@@ -2620,10 +3001,13 @@
       <c r="D127" s="1">
         <v>39042.51</v>
       </c>
-    </row>
-    <row r="128" spans="1:4">
+      <c r="E127" s="1">
+        <v>35482.47</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5">
       <c r="A128" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C128" s="1">
         <v>34066.12</v>
@@ -2631,10 +3015,13 @@
       <c r="D128" s="1">
         <v>35602.86</v>
       </c>
-    </row>
-    <row r="129" spans="1:4">
+      <c r="E128" s="1">
+        <v>33835.97</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5">
       <c r="A129" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C129" s="1">
         <v>36839.27</v>
@@ -2642,164 +3029,209 @@
       <c r="D129" s="1">
         <v>32746.36000000001</v>
       </c>
-    </row>
-    <row r="130" spans="1:4">
+      <c r="E129" s="1">
+        <v>32680.44</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5">
       <c r="A130" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C130" s="1">
-        <v>30392.57000000001</v>
+        <v>30392.57</v>
       </c>
       <c r="D130" s="1">
         <v>27323.19</v>
       </c>
-    </row>
-    <row r="131" spans="1:4">
+      <c r="E130" s="1">
+        <v>23731.72999999999</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5">
       <c r="A131" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C131" s="1">
         <v>38231.58</v>
       </c>
       <c r="D131" s="1">
-        <v>45711.41</v>
-      </c>
-    </row>
-    <row r="132" spans="1:4">
+        <v>45711.40999999999</v>
+      </c>
+      <c r="E131" s="1">
+        <v>38790.74</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5">
       <c r="A132" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C132" s="1">
         <v>72229.98999999999</v>
       </c>
       <c r="D132" s="1">
-        <v>71929.87999999998</v>
-      </c>
-    </row>
-    <row r="133" spans="1:4">
+        <v>72029.86999999998</v>
+      </c>
+      <c r="E132" s="1">
+        <v>62017.92</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5">
       <c r="A133" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C133" s="1">
         <v>8513.810000000001</v>
       </c>
       <c r="D133" s="1">
-        <v>8997.98</v>
-      </c>
-    </row>
-    <row r="134" spans="1:4">
+        <v>8997.980000000001</v>
+      </c>
+      <c r="E133" s="1">
+        <v>9747.689999999999</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5">
       <c r="A134" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C134" s="1">
-        <v>35911.41999999999</v>
+        <v>35911.42000000001</v>
       </c>
       <c r="D134" s="1">
-        <v>38868.65</v>
-      </c>
-    </row>
-    <row r="135" spans="1:4">
+        <v>38868.64999999999</v>
+      </c>
+      <c r="E134" s="1">
+        <v>37386.06</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5">
       <c r="A135" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C135" s="1">
-        <v>54393.83</v>
+        <v>54393.82999999998</v>
       </c>
       <c r="D135" s="1">
-        <v>55704.08000000001</v>
-      </c>
-    </row>
-    <row r="136" spans="1:4">
+        <v>55704.07999999999</v>
+      </c>
+      <c r="E135" s="1">
+        <v>52356.23000000001</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5">
       <c r="A136" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C136" s="1">
         <v>36957.98</v>
       </c>
       <c r="D136" s="1">
-        <v>35741.01</v>
-      </c>
-    </row>
-    <row r="137" spans="1:4">
+        <v>35741.01000000001</v>
+      </c>
+      <c r="E136" s="1">
+        <v>40668.92999999999</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5">
       <c r="A137" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C137" s="1">
-        <v>45803.21</v>
+        <v>45803.20999999999</v>
       </c>
       <c r="D137" s="1">
-        <v>39861.45999999999</v>
-      </c>
-    </row>
-    <row r="138" spans="1:4">
+        <v>40191.41</v>
+      </c>
+      <c r="E137" s="1">
+        <v>43911.57</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5">
       <c r="A138" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C138" s="1">
-        <v>25475.08</v>
+        <v>25475.08000000001</v>
       </c>
       <c r="D138" s="1">
         <v>24825.19</v>
       </c>
-    </row>
-    <row r="139" spans="1:4">
+      <c r="E138" s="1">
+        <v>18165.79</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5">
       <c r="A139" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C139" s="1">
         <v>49996.32000000001</v>
       </c>
       <c r="D139" s="1">
-        <v>54218.41000000001</v>
-      </c>
-    </row>
-    <row r="140" spans="1:4">
+        <v>54218.41</v>
+      </c>
+      <c r="E139" s="1">
+        <v>45493.55</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5">
       <c r="A140" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C140" s="1">
-        <v>48538.55000000001</v>
+        <v>48538.55</v>
       </c>
       <c r="D140" s="1">
-        <v>49157.07000000001</v>
-      </c>
-    </row>
-    <row r="141" spans="1:4">
+        <v>49157.07</v>
+      </c>
+      <c r="E140" s="1">
+        <v>43619.71</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5">
       <c r="A141" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C141" s="1">
-        <v>49564.45</v>
+        <v>49564.44999999998</v>
       </c>
       <c r="D141" s="1">
-        <v>38256.13000000001</v>
-      </c>
-    </row>
-    <row r="142" spans="1:4">
+        <v>38256.12999999998</v>
+      </c>
+      <c r="E141" s="1">
+        <v>49601.18999999999</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5">
       <c r="A142" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C142" s="1">
         <v>91004.63999999998</v>
       </c>
       <c r="D142" s="1">
-        <v>78764.78999999998</v>
-      </c>
-    </row>
-    <row r="143" spans="1:4">
+        <v>78764.78999999999</v>
+      </c>
+      <c r="E142" s="1">
+        <v>67782.51999999999</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5">
       <c r="A143" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C143" s="1">
-        <v>57224.7</v>
+        <v>57224.70000000001</v>
       </c>
       <c r="D143" s="1">
-        <v>54237.49999999999</v>
-      </c>
-    </row>
-    <row r="144" spans="1:4">
+        <v>54237.5</v>
+      </c>
+      <c r="E143" s="1">
+        <v>43999.16000000001</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5">
       <c r="A144" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C144" s="1">
         <v>31448.23000000001</v>
@@ -2807,10 +3239,13 @@
       <c r="D144" s="1">
         <v>27815.71</v>
       </c>
-    </row>
-    <row r="145" spans="1:4">
+      <c r="E144" s="1">
+        <v>29451.13</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5">
       <c r="A145" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C145" s="1">
         <v>18739.99</v>
@@ -2818,32 +3253,41 @@
       <c r="D145" s="1">
         <v>13582.96</v>
       </c>
-    </row>
-    <row r="146" spans="1:4">
+      <c r="E145" s="1">
+        <v>20723.67</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5">
       <c r="A146" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C146" s="1">
         <v>45222.85</v>
       </c>
       <c r="D146" s="1">
-        <v>43379.45000000001</v>
-      </c>
-    </row>
-    <row r="147" spans="1:4">
+        <v>43379.44999999999</v>
+      </c>
+      <c r="E146" s="1">
+        <v>47001.9</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5">
       <c r="A147" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C147" s="1">
-        <v>24827.87000000001</v>
+        <v>24827.87</v>
       </c>
       <c r="D147" s="1">
         <v>21690.06</v>
       </c>
-    </row>
-    <row r="148" spans="1:4">
+      <c r="E147" s="1">
+        <v>18576.6</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5">
       <c r="A148" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C148" s="1">
         <v>16859.43</v>
@@ -2851,10 +3295,13 @@
       <c r="D148" s="1">
         <v>12179.15</v>
       </c>
-    </row>
-    <row r="149" spans="1:4">
+      <c r="E148" s="1">
+        <v>14578.05</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5">
       <c r="A149" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C149" s="1">
         <v>35428.75</v>
@@ -2862,54 +3309,69 @@
       <c r="D149" s="1">
         <v>27937.64</v>
       </c>
-    </row>
-    <row r="150" spans="1:4">
+      <c r="E149" s="1">
+        <v>26504.88</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5">
       <c r="A150" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C150" s="1">
         <v>31301.67</v>
       </c>
       <c r="D150" s="1">
-        <v>32528.07000000001</v>
-      </c>
-    </row>
-    <row r="151" spans="1:4">
+        <v>32528.07</v>
+      </c>
+      <c r="E150" s="1">
+        <v>34443.03</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5">
       <c r="A151" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C151" s="1">
-        <v>83924.08999999998</v>
+        <v>83924.09</v>
       </c>
       <c r="D151" s="1">
         <v>67336.45999999999</v>
       </c>
-    </row>
-    <row r="152" spans="1:4">
+      <c r="E151" s="1">
+        <v>77649.77</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5">
       <c r="A152" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C152" s="1">
-        <v>15847.97000000001</v>
+        <v>15847.97</v>
       </c>
       <c r="D152" s="1">
         <v>13593.51</v>
       </c>
-    </row>
-    <row r="153" spans="1:4">
+      <c r="E152" s="1">
+        <v>12033.35</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5">
       <c r="A153" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C153" s="1">
-        <v>59323.87</v>
+        <v>59423.74</v>
       </c>
       <c r="D153" s="1">
         <v>66113.14</v>
       </c>
-    </row>
-    <row r="154" spans="1:4">
+      <c r="E153" s="1">
+        <v>65567.07000000001</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5">
       <c r="A154" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C154" s="1">
         <v>48373.71</v>
@@ -2917,10 +3379,13 @@
       <c r="D154" s="1">
         <v>43892.49000000001</v>
       </c>
-    </row>
-    <row r="155" spans="1:4">
+      <c r="E154" s="1">
+        <v>41487.71</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5">
       <c r="A155" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C155" s="1">
         <v>45460.27</v>
@@ -2928,98 +3393,125 @@
       <c r="D155" s="1">
         <v>39419.81</v>
       </c>
-    </row>
-    <row r="156" spans="1:4">
+      <c r="E155" s="1">
+        <v>35066.49000000001</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5">
       <c r="A156" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C156" s="1">
         <v>55087.41</v>
       </c>
       <c r="D156" s="1">
-        <v>58976.46000000001</v>
-      </c>
-    </row>
-    <row r="157" spans="1:4">
+        <v>59026.45</v>
+      </c>
+      <c r="E156" s="1">
+        <v>56863.85</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5">
       <c r="A157" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C157" s="1">
-        <v>72841.67999999999</v>
+        <v>72841.68000000001</v>
       </c>
       <c r="D157" s="1">
-        <v>66731.41999999998</v>
-      </c>
-    </row>
-    <row r="158" spans="1:4">
+        <v>66731.42</v>
+      </c>
+      <c r="E157" s="1">
+        <v>75919.99999999997</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5">
       <c r="A158" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C158" s="1">
-        <v>55993.95999999998</v>
+        <v>55993.96000000001</v>
       </c>
       <c r="D158" s="1">
-        <v>49814.87</v>
-      </c>
-    </row>
-    <row r="159" spans="1:4">
+        <v>49814.86999999999</v>
+      </c>
+      <c r="E158" s="1">
+        <v>52605.45</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5">
       <c r="A159" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C159" s="1">
-        <v>63405.88</v>
+        <v>63405.88000000003</v>
       </c>
       <c r="D159" s="1">
-        <v>46311.44</v>
-      </c>
-    </row>
-    <row r="160" spans="1:4">
+        <v>46311.43999999999</v>
+      </c>
+      <c r="E159" s="1">
+        <v>43366.58</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5">
       <c r="A160" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C160" s="1">
-        <v>37484.39</v>
+        <v>37484.39000000001</v>
       </c>
       <c r="D160" s="1">
-        <v>36864.79</v>
-      </c>
-    </row>
-    <row r="161" spans="1:4">
+        <v>36864.78999999999</v>
+      </c>
+      <c r="E160" s="1">
+        <v>33250.48</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5">
       <c r="A161" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C161" s="1">
-        <v>58828.36999999997</v>
+        <v>58828.37</v>
       </c>
       <c r="D161" s="1">
         <v>40513.49</v>
       </c>
-    </row>
-    <row r="162" spans="1:4">
+      <c r="E161" s="1">
+        <v>39010.31</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5">
       <c r="A162" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C162" s="1">
-        <v>64201.82</v>
+        <v>64201.81999999999</v>
       </c>
       <c r="D162" s="1">
-        <v>70019.10000000002</v>
-      </c>
-    </row>
-    <row r="163" spans="1:4">
+        <v>70019.09999999998</v>
+      </c>
+      <c r="E162" s="1">
+        <v>64695.09999999998</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5">
       <c r="A163" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C163" s="1">
         <v>58000.05</v>
       </c>
       <c r="D163" s="1">
-        <v>49095.89000000001</v>
-      </c>
-    </row>
-    <row r="164" spans="1:4">
+        <v>49095.88999999999</v>
+      </c>
+      <c r="E163" s="1">
+        <v>58247.60999999999</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5">
       <c r="A164" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C164" s="1">
         <v>19245.58</v>
@@ -3027,43 +3519,55 @@
       <c r="D164" s="1">
         <v>17130.33</v>
       </c>
-    </row>
-    <row r="165" spans="1:4">
+      <c r="E164" s="1">
+        <v>22522.8</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5">
       <c r="A165" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C165" s="1">
-        <v>29701.66000000001</v>
+        <v>29701.66</v>
       </c>
       <c r="D165" s="1">
         <v>23210.03</v>
       </c>
-    </row>
-    <row r="166" spans="1:4">
+      <c r="E165" s="1">
+        <v>26226.83</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5">
       <c r="A166" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C166" s="1">
-        <v>24082.24</v>
+        <v>24082.23999999999</v>
       </c>
       <c r="D166" s="1">
-        <v>17837.40999999999</v>
-      </c>
-    </row>
-    <row r="167" spans="1:4">
+        <v>17837.41</v>
+      </c>
+      <c r="E166" s="1">
+        <v>20097.83</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5">
       <c r="A167" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C167" s="1">
-        <v>45172.06</v>
+        <v>45172.06000000001</v>
       </c>
       <c r="D167" s="1">
         <v>44627.54</v>
       </c>
-    </row>
-    <row r="168" spans="1:4">
+      <c r="E167" s="1">
+        <v>49496.58</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5">
       <c r="A168" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C168" s="1">
         <v>28828.9</v>
@@ -3071,21 +3575,27 @@
       <c r="D168" s="1">
         <v>28605.17999999999</v>
       </c>
-    </row>
-    <row r="169" spans="1:4">
+      <c r="E168" s="1">
+        <v>24163.58</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5">
       <c r="A169" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C169" s="1">
         <v>131176.86</v>
       </c>
       <c r="D169" s="1">
-        <v>138459.91</v>
-      </c>
-    </row>
-    <row r="170" spans="1:4">
+        <v>138459.9099999999</v>
+      </c>
+      <c r="E169" s="1">
+        <v>146117.39</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5">
       <c r="A170" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C170" s="1">
         <v>16450.01</v>
@@ -3093,43 +3603,55 @@
       <c r="D170" s="1">
         <v>24717.84</v>
       </c>
-    </row>
-    <row r="171" spans="1:4">
+      <c r="E170" s="1">
+        <v>12550.9</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5">
       <c r="A171" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C171" s="1">
-        <v>84558.61999999997</v>
+        <v>84558.61999999994</v>
       </c>
       <c r="D171" s="1">
         <v>75316.01999999999</v>
       </c>
-    </row>
-    <row r="172" spans="1:4">
+      <c r="E171" s="1">
+        <v>107976.07</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5">
       <c r="A172" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C172" s="1">
-        <v>23166.21000000001</v>
+        <v>23166.21</v>
       </c>
       <c r="D172" s="1">
         <v>27351.61</v>
       </c>
-    </row>
-    <row r="173" spans="1:4">
+      <c r="E172" s="1">
+        <v>23614.73</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5">
       <c r="A173" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C173" s="1">
-        <v>36255.99</v>
+        <v>36255.99000000001</v>
       </c>
       <c r="D173" s="1">
-        <v>39159.49000000001</v>
-      </c>
-    </row>
-    <row r="174" spans="1:4">
+        <v>39159.48999999999</v>
+      </c>
+      <c r="E173" s="1">
+        <v>34546.46999999999</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5">
       <c r="A174" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C174" s="1">
         <v>66498.37999999999</v>
@@ -3137,21 +3659,27 @@
       <c r="D174" s="1">
         <v>60008.30999999999</v>
       </c>
-    </row>
-    <row r="175" spans="1:4">
+      <c r="E174" s="1">
+        <v>54878.74000000002</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5">
       <c r="A175" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C175" s="1">
-        <v>58881.39999999999</v>
+        <v>58881.4</v>
       </c>
       <c r="D175" s="1">
         <v>73030.25</v>
       </c>
-    </row>
-    <row r="176" spans="1:4">
+      <c r="E175" s="1">
+        <v>60030.31</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5">
       <c r="A176" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C176" s="1">
         <v>44881.42000000001</v>
@@ -3159,54 +3687,69 @@
       <c r="D176" s="1">
         <v>34567.37</v>
       </c>
-    </row>
-    <row r="177" spans="1:4">
+      <c r="E176" s="1">
+        <v>41391.09</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5">
       <c r="A177" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C177" s="1">
-        <v>52638.53999999999</v>
+        <v>52638.54</v>
       </c>
       <c r="D177" s="1">
-        <v>44572.92999999999</v>
-      </c>
-    </row>
-    <row r="178" spans="1:4">
+        <v>44572.93</v>
+      </c>
+      <c r="E177" s="1">
+        <v>55440.53000000003</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5">
       <c r="A178" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C178" s="1">
         <v>37204.7</v>
       </c>
       <c r="D178" s="1">
-        <v>32444.62000000001</v>
-      </c>
-    </row>
-    <row r="179" spans="1:4">
+        <v>32584.58000000001</v>
+      </c>
+      <c r="E178" s="1">
+        <v>32762.33000000001</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5">
       <c r="A179" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C179" s="1">
-        <v>28085.97</v>
+        <v>28085.96999999999</v>
       </c>
       <c r="D179" s="1">
         <v>26885.95</v>
       </c>
-    </row>
-    <row r="180" spans="1:4">
+      <c r="E179" s="1">
+        <v>22869.91</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5">
       <c r="A180" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C180" s="1">
-        <v>30051.5</v>
+        <v>30051.49999999999</v>
       </c>
       <c r="D180" s="1">
-        <v>30338.03000000001</v>
-      </c>
-    </row>
-    <row r="181" spans="1:4">
+        <v>30338.03</v>
+      </c>
+      <c r="E180" s="1">
+        <v>31748.03</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5">
       <c r="A181" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C181" s="1">
         <v>11884.24</v>
@@ -3214,98 +3757,125 @@
       <c r="D181" s="1">
         <v>13016.62</v>
       </c>
-    </row>
-    <row r="182" spans="1:4">
+      <c r="E181" s="1">
+        <v>12625.93</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5">
       <c r="A182" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C182" s="1">
-        <v>32543.45000000001</v>
+        <v>32543.45</v>
       </c>
       <c r="D182" s="1">
-        <v>32000.64</v>
-      </c>
-    </row>
-    <row r="183" spans="1:4">
+        <v>32000.64000000001</v>
+      </c>
+      <c r="E182" s="1">
+        <v>24636.76000000001</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5">
       <c r="A183" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C183" s="1">
-        <v>17408.24000000001</v>
+        <v>17408.24</v>
       </c>
       <c r="D183" s="1">
-        <v>21043.32999999999</v>
-      </c>
-    </row>
-    <row r="184" spans="1:4">
+        <v>21072.32</v>
+      </c>
+      <c r="E183" s="1">
+        <v>15218.41</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5">
       <c r="A184" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C184" s="1">
-        <v>22166.42</v>
+        <v>22166.42000000001</v>
       </c>
       <c r="D184" s="1">
-        <v>23712.67</v>
-      </c>
-    </row>
-    <row r="185" spans="1:4">
+        <v>23712.67000000001</v>
+      </c>
+      <c r="E184" s="1">
+        <v>19695.01</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5">
       <c r="A185" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C185" s="1">
-        <v>30418.24000000001</v>
+        <v>30418.24</v>
       </c>
       <c r="D185" s="1">
         <v>42215.38</v>
       </c>
-    </row>
-    <row r="186" spans="1:4">
+      <c r="E185" s="1">
+        <v>35712.92</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5">
       <c r="A186" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C186" s="1">
-        <v>29743.56</v>
+        <v>29743.55999999999</v>
       </c>
       <c r="D186" s="1">
         <v>34535.60999999999</v>
       </c>
-    </row>
-    <row r="187" spans="1:4">
+      <c r="E186" s="1">
+        <v>48114.09999999999</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5">
       <c r="A187" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C187" s="1">
-        <v>63482.89000000001</v>
+        <v>63482.89</v>
       </c>
       <c r="D187" s="1">
         <v>58893.77999999998</v>
       </c>
-    </row>
-    <row r="188" spans="1:4">
+      <c r="E187" s="1">
+        <v>56133.93000000001</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5">
       <c r="A188" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C188" s="1">
         <v>70807.74000000001</v>
       </c>
       <c r="D188" s="1">
-        <v>80193.26999999996</v>
-      </c>
-    </row>
-    <row r="189" spans="1:4">
+        <v>80193.26999999999</v>
+      </c>
+      <c r="E188" s="1">
+        <v>78255.61</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5">
       <c r="A189" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C189" s="1">
-        <v>35745.58</v>
+        <v>35745.57999999999</v>
       </c>
       <c r="D189" s="1">
-        <v>33704.10000000001</v>
-      </c>
-    </row>
-    <row r="190" spans="1:4">
+        <v>33704.1</v>
+      </c>
+      <c r="E189" s="1">
+        <v>28866.61</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5">
       <c r="A190" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C190" s="1">
         <v>37357.60999999999</v>
@@ -3313,10 +3883,13 @@
       <c r="D190" s="1">
         <v>38504.77000000001</v>
       </c>
-    </row>
-    <row r="191" spans="1:4">
+      <c r="E190" s="1">
+        <v>40709.43</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5">
       <c r="A191" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C191" s="1">
         <v>124323.94</v>
@@ -3324,32 +3897,41 @@
       <c r="D191" s="1">
         <v>113495.95</v>
       </c>
-    </row>
-    <row r="192" spans="1:4">
+      <c r="E191" s="1">
+        <v>117565.99</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5">
       <c r="A192" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C192" s="1">
-        <v>60277.96000000001</v>
+        <v>60277.96</v>
       </c>
       <c r="D192" s="1">
-        <v>56958.65000000002</v>
-      </c>
-    </row>
-    <row r="193" spans="1:4">
+        <v>56958.64999999999</v>
+      </c>
+      <c r="E192" s="1">
+        <v>70090.92</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5">
       <c r="A193" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C193" s="1">
         <v>32620.47</v>
       </c>
       <c r="D193" s="1">
-        <v>29516.66</v>
-      </c>
-    </row>
-    <row r="194" spans="1:4">
+        <v>29613.62000000001</v>
+      </c>
+      <c r="E193" s="1">
+        <v>29184.34</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5">
       <c r="A194" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C194" s="1">
         <v>19609.94</v>
@@ -3357,10 +3939,13 @@
       <c r="D194" s="1">
         <v>19074.8</v>
       </c>
-    </row>
-    <row r="195" spans="1:4">
+      <c r="E194" s="1">
+        <v>19461.68</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5">
       <c r="A195" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C195" s="1">
         <v>22587</v>
@@ -3368,43 +3953,55 @@
       <c r="D195" s="1">
         <v>24909.7</v>
       </c>
-    </row>
-    <row r="196" spans="1:4">
+      <c r="E195" s="1">
+        <v>26137.18</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5">
       <c r="A196" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C196" s="1">
-        <v>48774.51</v>
+        <v>48774.50999999999</v>
       </c>
       <c r="D196" s="1">
         <v>59876.95</v>
       </c>
-    </row>
-    <row r="197" spans="1:4">
+      <c r="E196" s="1">
+        <v>45376.86</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5">
       <c r="A197" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C197" s="1">
         <v>84139.86999999998</v>
       </c>
       <c r="D197" s="1">
-        <v>80855.01999999999</v>
-      </c>
-    </row>
-    <row r="198" spans="1:4">
+        <v>80855.01999999997</v>
+      </c>
+      <c r="E197" s="1">
+        <v>74686.38000000002</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5">
       <c r="A198" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C198" s="1">
         <v>56978.53999999998</v>
       </c>
       <c r="D198" s="1">
-        <v>52886.69</v>
-      </c>
-    </row>
-    <row r="199" spans="1:4">
+        <v>52886.69000000002</v>
+      </c>
+      <c r="E198" s="1">
+        <v>60106.92</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5">
       <c r="A199" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C199" s="1">
         <v>27272.34</v>
@@ -3412,10 +4009,13 @@
       <c r="D199" s="1">
         <v>34725.53000000001</v>
       </c>
-    </row>
-    <row r="200" spans="1:4">
+      <c r="E199" s="1">
+        <v>36090.76</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5">
       <c r="A200" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C200" s="1">
         <v>74082.27999999998</v>
@@ -3423,21 +4023,27 @@
       <c r="D200" s="1">
         <v>78901.42</v>
       </c>
-    </row>
-    <row r="201" spans="1:4">
+      <c r="E200" s="1">
+        <v>75545.77</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5">
       <c r="A201" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C201" s="1">
-        <v>56958.19999999998</v>
+        <v>56958.20000000001</v>
       </c>
       <c r="D201" s="1">
         <v>60860.39</v>
       </c>
-    </row>
-    <row r="202" spans="1:4">
+      <c r="E201" s="1">
+        <v>62081.97</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5">
       <c r="A202" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C202" s="1">
         <v>17654.32</v>
@@ -3445,43 +4051,55 @@
       <c r="D202" s="1">
         <v>17926.38</v>
       </c>
-    </row>
-    <row r="203" spans="1:4">
+      <c r="E202" s="1">
+        <v>22391.13000000001</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5">
       <c r="A203" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C203" s="1">
-        <v>28067.53000000001</v>
+        <v>28067.53</v>
       </c>
       <c r="D203" s="1">
-        <v>23739.00999999999</v>
-      </c>
-    </row>
-    <row r="204" spans="1:4">
+        <v>23739.01000000001</v>
+      </c>
+      <c r="E203" s="1">
+        <v>20446.44</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5">
       <c r="A204" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C204" s="1">
-        <v>125707.5299999999</v>
+        <v>125707.53</v>
       </c>
       <c r="D204" s="1">
-        <v>127762.26</v>
-      </c>
-    </row>
-    <row r="205" spans="1:4">
+        <v>128539.46</v>
+      </c>
+      <c r="E204" s="1">
+        <v>128375.5899999999</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5">
       <c r="A205" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C205" s="1">
         <v>28282.42</v>
       </c>
       <c r="D205" s="1">
-        <v>29125.16</v>
-      </c>
-    </row>
-    <row r="206" spans="1:4">
+        <v>29125.16000000001</v>
+      </c>
+      <c r="E205" s="1">
+        <v>31824.76</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5">
       <c r="A206" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C206" s="1">
         <v>29072.38</v>
@@ -3489,10 +4107,13 @@
       <c r="D206" s="1">
         <v>29557.43000000001</v>
       </c>
-    </row>
-    <row r="207" spans="1:4">
+      <c r="E206" s="1">
+        <v>23752.37</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5">
       <c r="A207" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C207" s="1">
         <v>9479.200000000001</v>
@@ -3500,21 +4121,27 @@
       <c r="D207" s="1">
         <v>9392.260000000002</v>
       </c>
-    </row>
-    <row r="208" spans="1:4">
+      <c r="E207" s="1">
+        <v>7178.5</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5">
       <c r="A208" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C208" s="1">
-        <v>26335.11000000001</v>
+        <v>26335.11</v>
       </c>
       <c r="D208" s="1">
-        <v>26557.02999999999</v>
-      </c>
-    </row>
-    <row r="209" spans="1:4">
+        <v>26864</v>
+      </c>
+      <c r="E208" s="1">
+        <v>28287.75</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5">
       <c r="A209" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C209" s="1">
         <v>26423.78</v>
@@ -3522,10 +4149,13 @@
       <c r="D209" s="1">
         <v>28588.63</v>
       </c>
-    </row>
-    <row r="210" spans="1:4">
+      <c r="E209" s="1">
+        <v>29899.93000000001</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5">
       <c r="A210" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C210" s="1">
         <v>23376.49</v>
@@ -3533,10 +4163,13 @@
       <c r="D210" s="1">
         <v>19123.28</v>
       </c>
-    </row>
-    <row r="211" spans="1:4">
+      <c r="E210" s="1">
+        <v>20044.52999999999</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5">
       <c r="A211" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C211" s="1">
         <v>21075.27</v>
@@ -3544,65 +4177,83 @@
       <c r="D211" s="1">
         <v>20125.78</v>
       </c>
-    </row>
-    <row r="212" spans="1:4">
+      <c r="E211" s="1">
+        <v>21292.37</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5">
       <c r="A212" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C212" s="1">
         <v>17248.97</v>
       </c>
       <c r="D212" s="1">
-        <v>18282.01</v>
-      </c>
-    </row>
-    <row r="213" spans="1:4">
+        <v>18282.01000000001</v>
+      </c>
+      <c r="E212" s="1">
+        <v>15826.14</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5">
       <c r="A213" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C213" s="1">
-        <v>28341.00000000001</v>
+        <v>28341</v>
       </c>
       <c r="D213" s="1">
-        <v>30204.63999999999</v>
-      </c>
-    </row>
-    <row r="214" spans="1:4">
+        <v>30204.64</v>
+      </c>
+      <c r="E213" s="1">
+        <v>26759.15999999999</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5">
       <c r="A214" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C214" s="1">
-        <v>27839.6</v>
+        <v>27839.59999999999</v>
       </c>
       <c r="D214" s="1">
         <v>25982.25</v>
       </c>
-    </row>
-    <row r="215" spans="1:4">
+      <c r="E214" s="1">
+        <v>22764.75</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5">
       <c r="A215" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C215" s="1">
-        <v>61858.17999999999</v>
+        <v>61858.18000000001</v>
       </c>
       <c r="D215" s="1">
-        <v>49346.68999999998</v>
-      </c>
-    </row>
-    <row r="216" spans="1:4">
+        <v>49443.68000000001</v>
+      </c>
+      <c r="E215" s="1">
+        <v>49433.88</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5">
       <c r="A216" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C216" s="1">
-        <v>27931.92</v>
+        <v>27931.92000000001</v>
       </c>
       <c r="D216" s="1">
-        <v>23257.87000000001</v>
-      </c>
-    </row>
-    <row r="217" spans="1:4">
+        <v>23257.87</v>
+      </c>
+      <c r="E216" s="1">
+        <v>22957.11</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5">
       <c r="A217" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C217" s="1">
         <v>12311.94</v>
@@ -3610,32 +4261,41 @@
       <c r="D217" s="1">
         <v>12810.86</v>
       </c>
-    </row>
-    <row r="218" spans="1:4">
+      <c r="E217" s="1">
+        <v>11183.11</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5">
       <c r="A218" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C218" s="1">
-        <v>32464.51999999999</v>
+        <v>32464.52000000001</v>
       </c>
       <c r="D218" s="1">
         <v>28799.82</v>
       </c>
-    </row>
-    <row r="219" spans="1:4">
+      <c r="E218" s="1">
+        <v>36550.02</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5">
       <c r="A219" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C219" s="1">
         <v>23681.4</v>
       </c>
       <c r="D219" s="1">
-        <v>23292.64999999999</v>
-      </c>
-    </row>
-    <row r="220" spans="1:4">
+        <v>23292.65000000001</v>
+      </c>
+      <c r="E219" s="1">
+        <v>25731.02</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5">
       <c r="A220" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C220" s="1">
         <v>16377.1</v>
@@ -3643,10 +4303,13 @@
       <c r="D220" s="1">
         <v>13137.1</v>
       </c>
-    </row>
-    <row r="221" spans="1:4">
+      <c r="E220" s="1">
+        <v>10436.99</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5">
       <c r="A221" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C221" s="1">
         <v>18031.7</v>
@@ -3654,43 +4317,55 @@
       <c r="D221" s="1">
         <v>21002.83</v>
       </c>
-    </row>
-    <row r="222" spans="1:4">
+      <c r="E221" s="1">
+        <v>20184.55000000001</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5">
       <c r="A222" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C222" s="1">
-        <v>19281.22999999999</v>
+        <v>19281.23</v>
       </c>
       <c r="D222" s="1">
-        <v>17477.38</v>
-      </c>
-    </row>
-    <row r="223" spans="1:4">
+        <v>17477.38000000001</v>
+      </c>
+      <c r="E222" s="1">
+        <v>22404.93</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5">
       <c r="A223" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C223" s="1">
         <v>16923.02</v>
       </c>
       <c r="D223" s="1">
-        <v>14428.49000000001</v>
-      </c>
-    </row>
-    <row r="224" spans="1:4">
+        <v>14428.49</v>
+      </c>
+      <c r="E223" s="1">
+        <v>14199.03</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5">
       <c r="A224" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C224" s="1">
-        <v>25868.19999999999</v>
+        <v>25868.2</v>
       </c>
       <c r="D224" s="1">
-        <v>23452.52000000001</v>
-      </c>
-    </row>
-    <row r="225" spans="1:4">
+        <v>23539.5</v>
+      </c>
+      <c r="E224" s="1">
+        <v>28282.16</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5">
       <c r="A225" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C225" s="1">
         <v>72049.13999999998</v>
@@ -3698,76 +4373,97 @@
       <c r="D225" s="1">
         <v>59842.84</v>
       </c>
-    </row>
-    <row r="226" spans="1:4">
+      <c r="E225" s="1">
+        <v>65633.43000000001</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5">
       <c r="A226" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C226" s="1">
-        <v>24263.80999999999</v>
+        <v>24263.81000000001</v>
       </c>
       <c r="D226" s="1">
         <v>24924.86</v>
       </c>
-    </row>
-    <row r="227" spans="1:4">
+      <c r="E226" s="1">
+        <v>25800.31</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5">
       <c r="A227" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C227" s="1">
-        <v>72816.91</v>
+        <v>72816.90999999999</v>
       </c>
       <c r="D227" s="1">
-        <v>82086.81</v>
-      </c>
-    </row>
-    <row r="228" spans="1:4">
+        <v>82086.80999999998</v>
+      </c>
+      <c r="E227" s="1">
+        <v>65935.42999999998</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5">
       <c r="A228" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C228" s="1">
-        <v>21516.72999999999</v>
+        <v>21516.73</v>
       </c>
       <c r="D228" s="1">
         <v>24098.03</v>
       </c>
-    </row>
-    <row r="229" spans="1:4">
+      <c r="E228" s="1">
+        <v>19355.29</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5">
       <c r="A229" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C229" s="1">
         <v>30938.8</v>
       </c>
       <c r="D229" s="1">
-        <v>29675.8</v>
-      </c>
-    </row>
-    <row r="230" spans="1:4">
+        <v>29675.79999999999</v>
+      </c>
+      <c r="E229" s="1">
+        <v>27073.4</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5">
       <c r="A230" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C230" s="1">
         <v>52514.02</v>
       </c>
       <c r="D230" s="1">
-        <v>52290.54</v>
-      </c>
-    </row>
-    <row r="231" spans="1:4">
+        <v>52290.53999999999</v>
+      </c>
+      <c r="E230" s="1">
+        <v>48702.69000000001</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5">
       <c r="A231" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C231" s="1">
-        <v>36096.59000000001</v>
+        <v>36096.59</v>
       </c>
       <c r="D231" s="1">
         <v>32898.64000000001</v>
       </c>
-    </row>
-    <row r="232" spans="1:4">
+      <c r="E231" s="1">
+        <v>31000.88</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5">
       <c r="A232" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C232" s="1">
         <v>22635.46</v>
@@ -3775,131 +4471,167 @@
       <c r="D232" s="1">
         <v>19470.8</v>
       </c>
-    </row>
-    <row r="233" spans="1:4">
+      <c r="E232" s="1">
+        <v>20012.14</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5">
       <c r="A233" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C233" s="1">
         <v>31055.44</v>
       </c>
       <c r="D233" s="1">
-        <v>34984.91000000001</v>
-      </c>
-    </row>
-    <row r="234" spans="1:4">
+        <v>34984.91</v>
+      </c>
+      <c r="E233" s="1">
+        <v>29097.72</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5">
       <c r="A234" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C234" s="1">
-        <v>26665.73000000001</v>
+        <v>26665.73</v>
       </c>
       <c r="D234" s="1">
         <v>26480.97</v>
       </c>
-    </row>
-    <row r="235" spans="1:4">
+      <c r="E234" s="1">
+        <v>30004.93</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5">
       <c r="A235" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C235" s="1">
-        <v>53643.11000000001</v>
+        <v>53643.10999999999</v>
       </c>
       <c r="D235" s="1">
         <v>34298.86</v>
       </c>
-    </row>
-    <row r="236" spans="1:4">
+      <c r="E235" s="1">
+        <v>37314.31000000001</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5">
       <c r="A236" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C236" s="1">
         <v>52556.48999999998</v>
       </c>
       <c r="D236" s="1">
-        <v>45059.90000000001</v>
-      </c>
-    </row>
-    <row r="237" spans="1:4">
+        <v>45231.21999999999</v>
+      </c>
+      <c r="E236" s="1">
+        <v>31421.35999999999</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5">
       <c r="A237" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C237" s="1">
-        <v>72816.68999999997</v>
+        <v>72816.69000000002</v>
       </c>
       <c r="D237" s="1">
-        <v>85398.86999999998</v>
-      </c>
-    </row>
-    <row r="238" spans="1:4">
+        <v>85398.87000000001</v>
+      </c>
+      <c r="E237" s="1">
+        <v>65694.58</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5">
       <c r="A238" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C238" s="1">
         <v>57148.15999999999</v>
       </c>
       <c r="D238" s="1">
-        <v>67177.87</v>
-      </c>
-    </row>
-    <row r="239" spans="1:4">
+        <v>67177.87000000001</v>
+      </c>
+      <c r="E238" s="1">
+        <v>52640.85</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5">
       <c r="A239" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C239" s="1">
-        <v>29008.38999999999</v>
+        <v>29008.39</v>
       </c>
       <c r="D239" s="1">
         <v>28531.9</v>
       </c>
-    </row>
-    <row r="240" spans="1:4">
+      <c r="E239" s="1">
+        <v>25323.72</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5">
       <c r="A240" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C240" s="1">
-        <v>42784.10000000001</v>
+        <v>42784.1</v>
       </c>
       <c r="D240" s="1">
         <v>35083.22</v>
       </c>
-    </row>
-    <row r="241" spans="1:4">
+      <c r="E240" s="1">
+        <v>43355.10999999999</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5">
       <c r="A241" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C241" s="1">
         <v>28920.21000000001</v>
       </c>
       <c r="D241" s="1">
-        <v>29141.09</v>
-      </c>
-    </row>
-    <row r="242" spans="1:4">
+        <v>29141.08999999999</v>
+      </c>
+      <c r="E241" s="1">
+        <v>27407.38</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5">
       <c r="A242" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C242" s="1">
-        <v>27465.96</v>
+        <v>27465.96000000001</v>
       </c>
       <c r="D242" s="1">
-        <v>32158.10000000001</v>
-      </c>
-    </row>
-    <row r="243" spans="1:4">
+        <v>32158.1</v>
+      </c>
+      <c r="E242" s="1">
+        <v>23119.79</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5">
       <c r="A243" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C243" s="1">
-        <v>37001.75</v>
+        <v>37001.74999999999</v>
       </c>
       <c r="D243" s="1">
-        <v>33889.94999999999</v>
-      </c>
-    </row>
-    <row r="244" spans="1:4">
+        <v>33889.95</v>
+      </c>
+      <c r="E243" s="1">
+        <v>30352.20000000001</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5">
       <c r="A244" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C244" s="1">
         <v>21241.9</v>
@@ -3907,65 +4639,83 @@
       <c r="D244" s="1">
         <v>19723.89</v>
       </c>
-    </row>
-    <row r="245" spans="1:4">
+      <c r="E244" s="1">
+        <v>13934.94</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5">
       <c r="A245" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C245" s="1">
-        <v>69996.87</v>
+        <v>69996.87000000001</v>
       </c>
       <c r="D245" s="1">
-        <v>63217.18999999997</v>
-      </c>
-    </row>
-    <row r="246" spans="1:4">
+        <v>63217.18999999999</v>
+      </c>
+      <c r="E245" s="1">
+        <v>61751.45</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5">
       <c r="A246" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C246" s="1">
-        <v>43277.13</v>
+        <v>43277.12999999999</v>
       </c>
       <c r="D246" s="1">
         <v>41732.49000000001</v>
       </c>
-    </row>
-    <row r="247" spans="1:4">
+      <c r="E246" s="1">
+        <v>45101.93</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5">
       <c r="A247" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C247" s="1">
-        <v>29585.14000000001</v>
+        <v>29585.13999999999</v>
       </c>
       <c r="D247" s="1">
-        <v>30374.1</v>
-      </c>
-    </row>
-    <row r="248" spans="1:4">
+        <v>30474.33000000001</v>
+      </c>
+      <c r="E247" s="1">
+        <v>32376.35999999999</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5">
       <c r="A248" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C248" s="1">
-        <v>72950.68999999999</v>
+        <v>72950.69000000002</v>
       </c>
       <c r="D248" s="1">
-        <v>60620.21999999999</v>
-      </c>
-    </row>
-    <row r="249" spans="1:4">
+        <v>61327.77</v>
+      </c>
+      <c r="E248" s="1">
+        <v>69942.01999999999</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5">
       <c r="A249" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C249" s="1">
-        <v>56805.01999999999</v>
+        <v>56805.02</v>
       </c>
       <c r="D249" s="1">
-        <v>53911.79</v>
-      </c>
-    </row>
-    <row r="250" spans="1:4">
+        <v>54088.26999999999</v>
+      </c>
+      <c r="E249" s="1">
+        <v>51187.08000000001</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5">
       <c r="A250" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C250" s="1">
         <v>35375.13</v>
@@ -3973,32 +4723,41 @@
       <c r="D250" s="1">
         <v>36913.37</v>
       </c>
-    </row>
-    <row r="251" spans="1:4">
+      <c r="E250" s="1">
+        <v>32875.04</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5">
       <c r="A251" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C251" s="1">
-        <v>82946.98999999998</v>
+        <v>82946.98999999996</v>
       </c>
       <c r="D251" s="1">
-        <v>85401.48</v>
-      </c>
-    </row>
-    <row r="252" spans="1:4">
+        <v>85401.47999999998</v>
+      </c>
+      <c r="E251" s="1">
+        <v>78861.61</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5">
       <c r="A252" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C252" s="1">
         <v>32832.46000000001</v>
       </c>
       <c r="D252" s="1">
-        <v>29476.14000000001</v>
-      </c>
-    </row>
-    <row r="253" spans="1:4">
+        <v>29476.14</v>
+      </c>
+      <c r="E252" s="1">
+        <v>31922.86000000001</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5">
       <c r="A253" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C253" s="1">
         <v>117044.94</v>
@@ -4006,43 +4765,55 @@
       <c r="D253" s="1">
         <v>125414.0699999999</v>
       </c>
-    </row>
-    <row r="254" spans="1:4">
+      <c r="E253" s="1">
+        <v>106582.39</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5">
       <c r="A254" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C254" s="1">
-        <v>25618.78000000001</v>
+        <v>25636.76</v>
       </c>
       <c r="D254" s="1">
-        <v>19660.98</v>
-      </c>
-    </row>
-    <row r="255" spans="1:4">
+        <v>19660.98000000001</v>
+      </c>
+      <c r="E254" s="1">
+        <v>18750.59</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5">
       <c r="A255" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C255" s="1">
         <v>17815.9</v>
       </c>
       <c r="D255" s="1">
-        <v>15322.48999999999</v>
-      </c>
-    </row>
-    <row r="256" spans="1:4">
+        <v>15322.49</v>
+      </c>
+      <c r="E255" s="1">
+        <v>15488.14</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5">
       <c r="A256" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C256" s="1">
-        <v>39904.91</v>
+        <v>39904.91000000001</v>
       </c>
       <c r="D256" s="1">
-        <v>32763.14999999999</v>
-      </c>
-    </row>
-    <row r="257" spans="1:4">
+        <v>32763.15</v>
+      </c>
+      <c r="E256" s="1">
+        <v>36049.34</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5">
       <c r="A257" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C257" s="1">
         <v>17033.96</v>
@@ -4050,21 +4821,27 @@
       <c r="D257" s="1">
         <v>17144.44</v>
       </c>
-    </row>
-    <row r="258" spans="1:4">
+      <c r="E257" s="1">
+        <v>16270.35</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5">
       <c r="A258" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C258" s="1">
-        <v>77420.56999999996</v>
+        <v>77420.56999999998</v>
       </c>
       <c r="D258" s="1">
-        <v>66117.8</v>
-      </c>
-    </row>
-    <row r="259" spans="1:4">
+        <v>66117.79999999999</v>
+      </c>
+      <c r="E258" s="1">
+        <v>86143.61999999995</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5">
       <c r="A259" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C259" s="1">
         <v>19982.69</v>
@@ -4072,170 +4849,218 @@
       <c r="D259" s="1">
         <v>17103.53</v>
       </c>
-    </row>
-    <row r="260" spans="1:4">
+      <c r="E259" s="1">
+        <v>13788.53</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5">
       <c r="A260" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C260" s="1">
         <v>37423.42000000001</v>
       </c>
       <c r="D260" s="1">
-        <v>38729.32000000001</v>
-      </c>
-    </row>
-    <row r="261" spans="1:4">
+        <v>38816.48000000001</v>
+      </c>
+      <c r="E260" s="1">
+        <v>36506.34000000001</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5">
       <c r="A261" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C261" s="1">
-        <v>29865.66</v>
+        <v>29865.66000000001</v>
       </c>
       <c r="D261" s="1">
-        <v>27622.02</v>
-      </c>
-    </row>
-    <row r="262" spans="1:4">
+        <v>27622.01999999999</v>
+      </c>
+      <c r="E261" s="1">
+        <v>27357.45</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5">
       <c r="A262" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C262" s="1">
         <v>46598.62</v>
       </c>
       <c r="D262" s="1">
-        <v>38968.85000000001</v>
-      </c>
-    </row>
-    <row r="263" spans="1:4">
+        <v>38968.85</v>
+      </c>
+      <c r="E262" s="1">
+        <v>44452.38999999999</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5">
       <c r="A263" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C263" s="1">
-        <v>59535.59999999998</v>
+        <v>59535.60000000001</v>
       </c>
       <c r="D263" s="1">
         <v>53171.47999999999</v>
       </c>
-    </row>
-    <row r="264" spans="1:4">
+      <c r="E263" s="1">
+        <v>63162.08000000002</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5">
       <c r="A264" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C264" s="1">
-        <v>27201.44999999999</v>
+        <v>27201.45</v>
       </c>
       <c r="D264" s="1">
-        <v>29426.61000000001</v>
-      </c>
-    </row>
-    <row r="265" spans="1:4">
+        <v>29426.61</v>
+      </c>
+      <c r="E264" s="1">
+        <v>27691.90999999999</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5">
       <c r="A265" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C265" s="1">
         <v>89352.58999999997</v>
       </c>
       <c r="D265" s="1">
-        <v>82527.90999999997</v>
-      </c>
-    </row>
-    <row r="266" spans="1:4">
+        <v>82527.90999999999</v>
+      </c>
+      <c r="E265" s="1">
+        <v>76213.01999999999</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5">
       <c r="A266" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C266" s="1">
-        <v>40280.46000000001</v>
+        <v>40280.46</v>
       </c>
       <c r="D266" s="1">
-        <v>39822.50999999999</v>
-      </c>
-    </row>
-    <row r="267" spans="1:4">
+        <v>39822.51</v>
+      </c>
+      <c r="E266" s="1">
+        <v>32261.19000000001</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5">
       <c r="A267" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C267" s="1">
-        <v>30894.82999999999</v>
+        <v>30894.83</v>
       </c>
       <c r="D267" s="1">
         <v>29380.69</v>
       </c>
-    </row>
-    <row r="268" spans="1:4">
+      <c r="E267" s="1">
+        <v>24983.13</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5">
       <c r="A268" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C268" s="1">
         <v>122438.3299999999</v>
       </c>
       <c r="D268" s="1">
-        <v>109823.59</v>
-      </c>
-    </row>
-    <row r="269" spans="1:4">
+        <v>109823.5899999999</v>
+      </c>
+      <c r="E268" s="1">
+        <v>112973.6699999999</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5">
       <c r="A269" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C269" s="1">
         <v>102093.96</v>
       </c>
       <c r="D269" s="1">
-        <v>102708.55</v>
-      </c>
-    </row>
-    <row r="270" spans="1:4">
+        <v>102807.11</v>
+      </c>
+      <c r="E269" s="1">
+        <v>106954.6599999999</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5">
       <c r="A270" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C270" s="1">
-        <v>38526.03000000001</v>
+        <v>38526.03</v>
       </c>
       <c r="D270" s="1">
-        <v>40263.57999999999</v>
-      </c>
-    </row>
-    <row r="271" spans="1:4">
+        <v>40263.58</v>
+      </c>
+      <c r="E270" s="1">
+        <v>44278.64</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5">
       <c r="A271" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C271" s="1">
         <v>37114.43000000001</v>
       </c>
       <c r="D271" s="1">
-        <v>34686.49</v>
-      </c>
-    </row>
-    <row r="272" spans="1:4">
+        <v>34686.49000000001</v>
+      </c>
+      <c r="E271" s="1">
+        <v>28598.07000000001</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5">
       <c r="A272" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C272" s="1">
         <v>11811.68</v>
       </c>
       <c r="D272" s="1">
-        <v>8326.189999999999</v>
-      </c>
-    </row>
-    <row r="273" spans="1:4">
+        <v>8326.190000000001</v>
+      </c>
+      <c r="E272" s="1">
+        <v>9095.32</v>
+      </c>
+    </row>
+    <row r="273" spans="1:5">
       <c r="A273" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D273" s="1">
         <v>2908.65</v>
       </c>
-    </row>
-    <row r="274" spans="1:4">
+      <c r="E273" s="1">
+        <v>1575.78</v>
+      </c>
+    </row>
+    <row r="274" spans="1:5">
       <c r="A274" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C274" s="1">
-        <v>7812.210000000001</v>
+        <v>7812.209999999999</v>
       </c>
       <c r="D274" s="1">
-        <v>9276.459999999999</v>
+        <v>9276.460000000001</v>
+      </c>
+      <c r="E274" s="1">
+        <v>5915.760000000001</v>
       </c>
     </row>
   </sheetData>
